--- a/Delta Option Chain/source/eth_chain.xlsx
+++ b/Delta Option Chain/source/eth_chain.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +492,16 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Total strikes - edit A2</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
